--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE71BC36-449F-4B51-B849-B80BF4E9269C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D40E977-CA4B-4E2C-AD50-5EB6E1BE931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
+    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックス（UI）テスト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -586,6 +586,20 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門登録単体UIテスト 須崎千穂子</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手順No</t>
+    <rPh sb="0" eb="2">
+      <t>テジュン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -633,7 +647,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -642,6 +656,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -671,7 +688,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3132931</xdr:colOff>
+      <xdr:colOff>3136106</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>572943</xdr:rowOff>
     </xdr:to>
@@ -715,9 +732,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>10745</xdr:colOff>
+      <xdr:colOff>7570</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>635000</xdr:rowOff>
+      <xdr:rowOff>638175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -759,9 +776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3394364</xdr:colOff>
+      <xdr:colOff>3397539</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>566025</xdr:rowOff>
+      <xdr:rowOff>562850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -803,9 +820,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3362775</xdr:colOff>
+      <xdr:colOff>3359600</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>623456</xdr:rowOff>
+      <xdr:rowOff>620281</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -849,7 +866,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>3317777</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>565729</xdr:rowOff>
+      <xdr:rowOff>562554</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -891,9 +908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3394364</xdr:colOff>
+      <xdr:colOff>3397539</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>566024</xdr:rowOff>
+      <xdr:rowOff>562849</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -935,7 +952,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>5690</xdr:colOff>
+      <xdr:colOff>8865</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -981,7 +998,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>96312</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>600364</xdr:rowOff>
+      <xdr:rowOff>597189</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1023,7 +1040,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>80634</xdr:colOff>
+      <xdr:colOff>83809</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>591186</xdr:rowOff>
     </xdr:to>
@@ -1067,7 +1084,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3416905</xdr:colOff>
+      <xdr:colOff>3420080</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>726429</xdr:rowOff>
     </xdr:to>
@@ -1111,7 +1128,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3376587</xdr:colOff>
+      <xdr:colOff>3379762</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>478054</xdr:rowOff>
     </xdr:to>
@@ -1446,16 +1463,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717FA1E3-7A6E-499A-9111-A7EF82F47CA1}">
-  <dimension ref="A2:D13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.58203125" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="78.33203125" customWidth="1"/>
     <col min="3" max="3" width="44.1640625" customWidth="1"/>
     <col min="4" max="4" width="45.9140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1585,6 +1612,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D40E977-CA4B-4E2C-AD50-5EB6E1BE931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4005B47C-DE99-4D7C-8FE9-D2C505CB41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="15720" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックス（UI）テスト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="64">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -106,13 +106,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>20文字以内で入力してください。とエラーが出る。</t>
-    <rPh sb="21" eb="22">
-      <t>デ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認画面に遷移する。</t>
     <rPh sb="0" eb="2">
       <t>カクニン</t>
@@ -486,42 +479,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門名を空欄で完了ボタンを押す</t>
-    <rPh sb="4" eb="6">
-      <t>クウラン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門名は入力必須です。とエラーが出る。</t>
-    <rPh sb="4" eb="8">
-      <t>ニュウリョクヒッス</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>デ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門名に「あいうえおかきくけこさしすせそたちつてとな」を入力して完了ボタンを押す</t>
-    <rPh sb="28" eb="30">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門名に「情報システム部」を入力して完了ボタンを押す</t>
     <rPh sb="5" eb="7">
       <t>ジョウホウ</t>
@@ -600,6 +557,225 @@
     <t>手順No</t>
     <rPh sb="0" eb="2">
       <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常系を用いて一通り登録できる流れのチェック</t>
+    <rPh sb="1" eb="4">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒトトオ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③部署名の文字数チェック（正常系の境界値：20文字）</t>
+    <rPh sb="1" eb="4">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>セイジョウケイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>キョウカイチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④部署名の文字数チェック（異常系の境界値：21文字）</t>
+    <rPh sb="1" eb="4">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>キョウカイチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常系を用いて一通り登録できる流れのチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門名に「情報システム部」を入力して完了ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ブモンメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②部署名の入力必須エラーが正しく出るかチェック</t>
+    <rPh sb="1" eb="4">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②部署名の入力必須エラーが正しく出るかチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>③部署名の文字数チェック（正常系の境界値：20文字）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>④部署名の文字数チェック（異常系の境界値：21文字）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名を空白のまま完了ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クウハク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名：入力必須です。
+とエラーが出る</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名「あいうえおかきくけこさしすせそたちつてと」と入力して完了ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名「あいうえおかきくけこさしすせそたちつてとな」と入力して完了ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名：20文字以内に入力してください。
+とエラーが出る</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>デ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -608,7 +784,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,13 +800,28 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -642,12 +833,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -660,8 +854,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -675,495 +876,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3136106</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>572943</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44ABADC2-9BC6-CDF9-2DA5-EFA68BF12D86}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9683750" y="444500"/>
-          <a:ext cx="3132931" cy="555625"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>7570</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>638175</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1307149E-4D16-905C-B0C1-9ED8B86C2E70}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="1212273"/>
-          <a:ext cx="3509018" cy="635000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3397539</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>562850</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EAB12B-F2D7-58A5-2324-13EF0AB6D43B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="2713183"/>
-          <a:ext cx="3394364" cy="566024"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3359600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>620281</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89D4B3BB-F1E5-1688-FB62-8CC1B5850884}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="1962727"/>
-          <a:ext cx="3362775" cy="623456"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3317777</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>562554</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB799BA-7FDC-FA35-697A-329D116D00F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="3463637"/>
-          <a:ext cx="3317777" cy="565728"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3397539</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>562849</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C308FA2D-6226-4853-B1B1-EADFB1ED4CF1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="4214091"/>
-          <a:ext cx="3394364" cy="566024"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>8865</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3CC6B4-D747-ACB3-3B5C-717CDA3E060A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="4964545"/>
-          <a:ext cx="3503963" cy="750455"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>96312</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>597189</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F00D6F1-23A1-6411-5275-66132C1A4656}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686636" y="5715000"/>
-          <a:ext cx="3594585" cy="600364"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>83809</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>591186</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53CE2DCA-141F-9BCF-7C5B-D474C09F1649}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686271" y="6430635"/>
-          <a:ext cx="3578173" cy="591186"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3420080</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>726429</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7198A9A4-EC1A-387D-498B-F074038C577F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686270" y="7176509"/>
-          <a:ext cx="3416905" cy="726428"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3379762</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>478054</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90B1BE0C-51A8-2B5B-2C0A-478460207705}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9686270" y="7922381"/>
-          <a:ext cx="3376587" cy="478054"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1463,161 +1175,331 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717FA1E3-7A6E-499A-9111-A7EF82F47CA1}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="78.33203125" customWidth="1"/>
     <col min="3" max="3" width="44.1640625" customWidth="1"/>
     <col min="4" max="4" width="45.9140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="10" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-    </row>
+    <row r="26" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="30" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="31" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="32" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="33" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="34" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="35" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="36" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="37" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A3" location="'ブラックボックス（UI）テスト'!A8" display="①正常系を用いて一通り登録できる流れのチェック" xr:uid="{44B7A849-4F82-4B1A-9353-B147EE06218D}"/>
+    <hyperlink ref="A4" location="'ブラックボックス（UI）テスト'!A20" display="②部署名の入力必須エラーが正しく出るかチェック" xr:uid="{88A8C6D5-0BB4-4C29-8BB6-398F9DBCCFC7}"/>
+    <hyperlink ref="A5" location="'ブラックボックス（UI）テスト'!A23" display="③部署名の文字数チェック（正常系の境界値：20文字）" xr:uid="{D9C9E4F4-656B-4DA3-A3E0-2F16427B793A}"/>
+    <hyperlink ref="A6" location="'ブラックボックス（UI）テスト'!A26" display="④部署名の文字数チェック（異常系の境界値：21文字）" xr:uid="{5C18BC10-7548-4C5F-A832-F9AC899187F2}"/>
+    <hyperlink ref="E8" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
+    <hyperlink ref="E20" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
+    <hyperlink ref="E23" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
+    <hyperlink ref="E26" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1634,216 +1516,216 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4005B47C-DE99-4D7C-8FE9-D2C505CB41C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8790534-9F46-4406-8B5F-66ECD89B4459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックス（UI）テスト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -151,22 +151,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>手順4と同様、確認画面に遷移する。</t>
-    <rPh sb="0" eb="2">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウヨウ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>カクニンガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門登録(完了)画面に遷移する</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
@@ -474,25 +458,6 @@
       <t>ジョウブ</t>
     </rPh>
     <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門名に「情報システム部」を入力して完了ボタンを押す</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -776,6 +741,22 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手順2と同様、確認画面に遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -851,14 +832,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -876,6 +857,671 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>80635</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1460391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99BD5623-DF04-91EE-2DBD-CF003D720DB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="2519842"/>
+          <a:ext cx="3578175" cy="1460390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>151191</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1324811</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED02AEB-43C5-5302-B573-68FB44E0CFA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="4051906"/>
+          <a:ext cx="3648730" cy="1324810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>200743</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1511905</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE2B769-9AC8-8237-3907-C2929B0AA181}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="5583968"/>
+          <a:ext cx="3698283" cy="1511905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3494171</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1320397</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FEAB903-A8F6-2097-ACB5-C0561BB48017}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="7116032"/>
+          <a:ext cx="3494170" cy="1320397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2751489</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1411111</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27888DC4-F4B4-96C1-387B-6D94AFA72416}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="8648095"/>
+          <a:ext cx="2751489" cy="1411111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3356429</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1349153</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C7141D6-3B6A-8551-7897-AB644DD58F21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="10180159"/>
+          <a:ext cx="3356429" cy="1349153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3467303</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1346979</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F95A2F6-E0B4-5408-D934-6084FD4FE48E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="11712222"/>
+          <a:ext cx="3467302" cy="1346979"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2956015</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1481667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A98BCA3-9817-A11E-61D4-A2140B364740}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="13244287"/>
+          <a:ext cx="2956015" cy="1481666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>41878</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>846667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B71850-3455-AE77-CB1B-DEB166B4DFFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="14776349"/>
+          <a:ext cx="3539417" cy="846667"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3426984</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1391690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43125989-080D-27C7-1BB1-DDDB2EEACA89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="17054286"/>
+          <a:ext cx="3426984" cy="1391690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3426984</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1391690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE723F9-72F3-4C32-BD3F-4E7FD3EC0A78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="20803810"/>
+          <a:ext cx="3426984" cy="1391690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3426984</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1391690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28C9FD5E-0E85-48D1-A225-8BA92ADE42CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="24553333"/>
+          <a:ext cx="3426984" cy="1391690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3459609</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1431271</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{478C38B5-9040-D77F-CD0C-11CB95EB6FBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="18556112"/>
+          <a:ext cx="3459609" cy="1431270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>20159</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1344619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61156D80-1104-2C05-D570-57AA1F3DAB7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="22305635"/>
+          <a:ext cx="3517698" cy="1344619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3306032</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1386663</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4669D502-430F-B744-9B19-714299C565FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="26055159"/>
+          <a:ext cx="3306032" cy="1386663"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1175,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717FA1E3-7A6E-499A-9111-A7EF82F47CA1}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -1186,47 +1832,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
-        <v>48</v>
+      <c r="A3" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5" t="s">
-        <v>53</v>
+      <c r="A4" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5" t="s">
-        <v>49</v>
+      <c r="A5" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5" t="s">
-        <v>50</v>
+      <c r="A6" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1238,19 +1884,19 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5" t="s">
-        <v>57</v>
+      <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -1262,215 +1908,205 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>8</v>
       </c>
       <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="18" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4" t="s">
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
         <v>1</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B26" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
         <v>2</v>
       </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B27" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
+    </row>
+    <row r="28" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="29" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="30" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="31" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -1478,15 +2114,14 @@
     <row r="33" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="34" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="35" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="36" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -1495,11 +2130,12 @@
     <hyperlink ref="A5" location="'ブラックボックス（UI）テスト'!A23" display="③部署名の文字数チェック（正常系の境界値：20文字）" xr:uid="{D9C9E4F4-656B-4DA3-A3E0-2F16427B793A}"/>
     <hyperlink ref="A6" location="'ブラックボックス（UI）テスト'!A26" display="④部署名の文字数チェック（異常系の境界値：21文字）" xr:uid="{5C18BC10-7548-4C5F-A832-F9AC899187F2}"/>
     <hyperlink ref="E8" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
-    <hyperlink ref="E20" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
-    <hyperlink ref="E23" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
-    <hyperlink ref="E26" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
+    <hyperlink ref="E19" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
+    <hyperlink ref="E22" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
+    <hyperlink ref="E25" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1516,216 +2152,216 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
         <v>21</v>
       </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8790534-9F46-4406-8B5F-66ECD89B4459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4771AC-B634-4AF6-9FFC-6BECFB165B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
   <sheets>
     <sheet name="ブラックボックス（UI）テスト" sheetId="1" r:id="rId1"/>
-    <sheet name="Repositoryのホワイトボックステスト" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -176,263 +175,6 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対象リポジトリ</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>対象メソッド</t>
-    <rPh sb="0" eb="2">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>条件</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>期待結果</t>
-    <rPh sb="0" eb="2">
-      <t>キタイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テスト判定</t>
-    <rPh sb="3" eb="5">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Department</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FindAll</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に何も入っていないとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>InternalExceptionを返す</t>
-    <rPh sb="18" eb="19">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>○</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FindById</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力したidに合致する部署が存在するとき</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガッチ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>該当部署を取得する</t>
-    <rPh sb="0" eb="4">
-      <t>ガイトウブショ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力したidに合致する部署が存在しないとき</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガッチ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に部署が入っているとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象と同じ部署を取得する</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ブショ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Employee</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Create</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>すでに存在している社員をAddしたとき</t>
-    <rPh sb="3" eb="5">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>探索対象に社員が入っているとき</t>
-    <rPh sb="0" eb="4">
-      <t>タンサクタイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>未登録の社員をAddしたとき</t>
-    <rPh sb="0" eb="3">
-      <t>ミトウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シャイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社員が追加され追加社員も含めて社員情報が合致する</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガッチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>備考</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>従業員登録の部分と同様</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ドウヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>すでに存在している部門をAddしたとき</t>
-    <rPh sb="3" eb="5">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>未登録の部門をAddしたとき</t>
-    <rPh sb="0" eb="3">
-      <t>ミトウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブモン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -757,6 +499,55 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑤部署名の重複チェック</t>
+    <rPh sb="1" eb="4">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名「総務部」と入力して完了ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ブショメイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ソウムブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ名前の部署がすでに存在しています。
+とエラーが出る</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>デ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -865,13 +656,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>80635</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1460391</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -909,13 +700,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>151191</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1324811</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -953,13 +744,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>200743</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1511905</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -997,13 +788,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3494171</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1320397</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1041,13 +832,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2751489</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1411111</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1085,13 +876,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3356429</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1349153</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1129,13 +920,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3467303</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1346979</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1173,13 +964,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2956015</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1481667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1217,13 +1008,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>41878</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>846667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1261,13 +1052,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1391690</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1305,13 +1096,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>1391690</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1349,13 +1140,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1391690</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1393,13 +1184,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3459609</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1431271</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1437,13 +1228,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>20159</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>1344619</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1481,13 +1272,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>3306032</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>1386663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1513,6 +1304,89 @@
         <a:xfrm>
           <a:off x="9968492" y="26055159"/>
           <a:ext cx="3306032" cy="1386663"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3426984" cy="1391690"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E60C254-C644-4BFE-931A-51BBB4DF7BF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="24785159"/>
+          <a:ext cx="3426984" cy="1391690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>710611</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E4969A1-C655-5FD0-6BCB-A9F5EA62CB67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968493" y="30006270"/>
+          <a:ext cx="3497539" cy="710611"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1821,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717FA1E3-7A6E-499A-9111-A7EF82F47CA1}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -1833,14 +1707,14 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1848,7 +1722,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1856,7 +1730,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1864,7 +1738,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1872,256 +1746,295 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
         <v>9</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>38</v>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
         <v>2</v>
       </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
         <v>2</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
+    <row r="26" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
         <v>2</v>
       </c>
-      <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="32" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="33" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="34" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="35" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="36" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="37" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -2129,243 +2042,14 @@
     <hyperlink ref="A4" location="'ブラックボックス（UI）テスト'!A20" display="②部署名の入力必須エラーが正しく出るかチェック" xr:uid="{88A8C6D5-0BB4-4C29-8BB6-398F9DBCCFC7}"/>
     <hyperlink ref="A5" location="'ブラックボックス（UI）テスト'!A23" display="③部署名の文字数チェック（正常系の境界値：20文字）" xr:uid="{D9C9E4F4-656B-4DA3-A3E0-2F16427B793A}"/>
     <hyperlink ref="A6" location="'ブラックボックス（UI）テスト'!A26" display="④部署名の文字数チェック（異常系の境界値：21文字）" xr:uid="{5C18BC10-7548-4C5F-A832-F9AC899187F2}"/>
-    <hyperlink ref="E8" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
-    <hyperlink ref="E19" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
-    <hyperlink ref="E22" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
-    <hyperlink ref="E25" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
+    <hyperlink ref="E9" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
+    <hyperlink ref="E20" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
+    <hyperlink ref="E23" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
+    <hyperlink ref="E26" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
+    <hyperlink ref="E29" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5BBD1C52-098F-40DA-88A4-50C39110E03A}"/>
+    <hyperlink ref="A7" location="'ブラックボックス（UI）テスト'!A29" display="⑤部署名の重複チェック" xr:uid="{8EDA1AC3-5459-426F-983A-9291D61AB0A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD1633D-FC32-4706-9F40-0B209A1EE2A3}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="47.6640625" customWidth="1"/>
-    <col min="4" max="4" width="34.1640625" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4771AC-B634-4AF6-9FFC-6BECFB165B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61D0723-11EE-4B4B-9CC7-3CE281A4E5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -90,16 +90,6 @@
       <t>トウロク</t>
     </rPh>
     <rPh sb="6" eb="7">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メニューに戻るボタンを押す</t>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="11" eb="12">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -548,6 +538,41 @@
     </rPh>
     <rPh sb="25" eb="26">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥ホーム画面の部門一覧から新規登録に遷移</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>シンキトウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧を確認するボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -626,10 +651,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -656,21 +681,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>80635</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1460391</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2842381</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>909675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="18" name="図 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99BD5623-DF04-91EE-2DBD-CF003D720DB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B591E3-1D13-796D-9B6E-48C22C8A319F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -686,8 +711,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="2519842"/>
-          <a:ext cx="3578175" cy="1460390"/>
+          <a:off x="9968492" y="2771825"/>
+          <a:ext cx="2842381" cy="909675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -699,22 +724,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>151191</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1324811</xdr:rowOff>
+      <xdr:colOff>30238</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>867654</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="20" name="図 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED02AEB-43C5-5302-B573-68FB44E0CFA2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6485023-2FAE-05B9-5C90-DB41192647CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -730,8 +755,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="4051906"/>
-          <a:ext cx="3648730" cy="1324810"/>
+          <a:off x="9968492" y="4303889"/>
+          <a:ext cx="2902857" cy="867654"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -744,21 +769,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>200743</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1511905</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2812143</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>916635</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="21" name="図 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE2B769-9AC8-8237-3907-C2929B0AA181}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D21A306-0B53-0EE2-92CE-A04E2CBD910C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -774,8 +799,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="5583968"/>
-          <a:ext cx="3698283" cy="1511905"/>
+          <a:off x="9968492" y="5835953"/>
+          <a:ext cx="2812143" cy="916634"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -787,22 +812,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3494171</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1320397</xdr:rowOff>
+      <xdr:colOff>2812143</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>859818</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="22" name="図 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FEAB903-A8F6-2097-ACB5-C0561BB48017}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC7B8853-F4A9-C79A-71D1-B50FFC35BE23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -818,8 +843,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="7116032"/>
-          <a:ext cx="3494170" cy="1320397"/>
+          <a:off x="9968492" y="7368016"/>
+          <a:ext cx="2812143" cy="859818"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -832,21 +857,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2751489</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1411111</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>10079</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1150183</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27888DC4-F4B4-96C1-387B-6D94AFA72416}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98D2D0F1-C46B-4310-5561-F31BA2278F09}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -862,8 +887,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="8648095"/>
-          <a:ext cx="2751489" cy="1411111"/>
+          <a:off x="9968492" y="8900080"/>
+          <a:ext cx="2882698" cy="1150182"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -876,21 +901,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3356429</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1349153</xdr:rowOff>
+      <xdr:colOff>2758586</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>846667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C7141D6-3B6A-8551-7897-AB644DD58F21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C3C454B-CFB3-072B-16D6-484C804F899F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -906,8 +931,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="10180159"/>
-          <a:ext cx="3356429" cy="1349153"/>
+          <a:off x="9968492" y="10432143"/>
+          <a:ext cx="2758586" cy="846667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -919,22 +944,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>131031</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>141111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3467303</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1346979</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>40317</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1267320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F95A2F6-E0B4-5408-D934-6084FD4FE48E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159E21D2-3285-EB5A-6941-8572E05838CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -950,8 +975,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="11712222"/>
-          <a:ext cx="3467302" cy="1346979"/>
+          <a:off x="10099523" y="13637381"/>
+          <a:ext cx="2781905" cy="1126209"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -963,22 +988,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2956015</xdr:colOff>
+      <xdr:colOff>2802065</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1481667</xdr:rowOff>
+      <xdr:rowOff>943495</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A98BCA3-9817-A11E-61D4-A2140B364740}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82412039-80EC-F0DE-9431-10009A9F6381}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -994,8 +1019,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="13244287"/>
-          <a:ext cx="2956015" cy="1481666"/>
+          <a:off x="9968493" y="11964207"/>
+          <a:ext cx="2802064" cy="943494"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1007,22 +1032,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>41878</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>846667</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2060223</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1471589</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B71850-3455-AE77-CB1B-DEB166B4DFFF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6CC79F0-157A-39F5-5AA2-15EF00861EDE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1038,8 +1063,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="14776349"/>
-          <a:ext cx="3539417" cy="846667"/>
+          <a:off x="9968492" y="15028334"/>
+          <a:ext cx="2060223" cy="1471588"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1052,21 +1077,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1391690</xdr:rowOff>
+      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>970145</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43125989-080D-27C7-1BB1-DDDB2EEACA89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302B3641-2E1D-300B-256B-8730FC234488}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1082,8 +1107,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="17054286"/>
-          <a:ext cx="3426984" cy="1391690"/>
+          <a:off x="9968492" y="17054287"/>
+          <a:ext cx="2791984" cy="970144"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1096,21 +1121,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1391690</xdr:rowOff>
+      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>970144</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE723F9-72F3-4C32-BD3F-4E7FD3EC0A78}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{156B6D19-56BD-45B9-A39A-28F60A937B9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1126,8 +1151,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="20803810"/>
-          <a:ext cx="3426984" cy="1391690"/>
+          <a:off x="9968492" y="20491349"/>
+          <a:ext cx="2791984" cy="970144"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1140,21 +1165,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3426984</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1391690</xdr:rowOff>
+      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>970144</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28C9FD5E-0E85-48D1-A225-8BA92ADE42CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F10C29B-5AD0-45D1-92A3-D64ED651E16C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1170,8 +1195,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="24553333"/>
-          <a:ext cx="3426984" cy="1391690"/>
+          <a:off x="9968492" y="24109841"/>
+          <a:ext cx="2791984" cy="970144"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1184,21 +1209,65 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3459609</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1431271</xdr:rowOff>
+      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>970144</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{478C38B5-9040-D77F-CD0C-11CB95EB6FBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8145721C-2306-4562-AE84-F6D8C9090021}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9968492" y="27657778"/>
+          <a:ext cx="2791984" cy="970144"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2852460</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>862833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32AB8BB9-E74A-6849-6A3D-F29047FFCCB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1214,8 +1283,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="18556112"/>
-          <a:ext cx="3459609" cy="1431270"/>
+          <a:off x="9968493" y="21993175"/>
+          <a:ext cx="2852459" cy="862833"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1227,22 +1296,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>20159</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1344619</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1172841</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
+        <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61156D80-1104-2C05-D570-57AA1F3DAB7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD72C78-2421-9029-6076-9A2349AB8CE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1258,8 +1327,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="22305635"/>
-          <a:ext cx="3517698" cy="1344619"/>
+          <a:off x="9968492" y="25611667"/>
+          <a:ext cx="2791984" cy="1172841"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1271,22 +1340,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3306032</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>1386663</xdr:rowOff>
+      <xdr:colOff>2852460</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1221109</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4669D502-430F-B744-9B19-714299C565FD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030ECC85-1981-98E8-82AB-507CBB286C66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1302,91 +1371,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="26055159"/>
-          <a:ext cx="3306032" cy="1386663"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3426984" cy="1391690"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E60C254-C644-4BFE-931A-51BBB4DF7BF1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9968492" y="24785159"/>
-          <a:ext cx="3426984" cy="1391690"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>710611</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E4969A1-C655-5FD0-6BCB-A9F5EA62CB67}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9968493" y="30006270"/>
-          <a:ext cx="3497539" cy="710611"/>
+          <a:off x="9968493" y="29129365"/>
+          <a:ext cx="2852459" cy="1221109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1695,26 +1681,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717FA1E3-7A6E-499A-9111-A7EF82F47CA1}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="78.33203125" customWidth="1"/>
     <col min="3" max="3" width="44.1640625" customWidth="1"/>
-    <col min="4" max="4" width="45.9140625" customWidth="1"/>
+    <col min="4" max="4" width="37.75" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1722,7 +1708,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1730,7 +1716,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1738,7 +1724,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1746,7 +1732,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1754,287 +1740,295 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
         <v>9</v>
       </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
         <v>2</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>12</v>
+    </row>
+    <row r="24" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5" t="s">
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="48.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
         <v>2</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
+    </row>
+    <row r="30" spans="1:5" ht="42.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
         <v>2</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    </row>
     <row r="33" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="34" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="35" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="36" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="37" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="38" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A27:D27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -2042,11 +2036,11 @@
     <hyperlink ref="A4" location="'ブラックボックス（UI）テスト'!A20" display="②部署名の入力必須エラーが正しく出るかチェック" xr:uid="{88A8C6D5-0BB4-4C29-8BB6-398F9DBCCFC7}"/>
     <hyperlink ref="A5" location="'ブラックボックス（UI）テスト'!A23" display="③部署名の文字数チェック（正常系の境界値：20文字）" xr:uid="{D9C9E4F4-656B-4DA3-A3E0-2F16427B793A}"/>
     <hyperlink ref="A6" location="'ブラックボックス（UI）テスト'!A26" display="④部署名の文字数チェック（異常系の境界値：21文字）" xr:uid="{5C18BC10-7548-4C5F-A832-F9AC899187F2}"/>
-    <hyperlink ref="E9" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
-    <hyperlink ref="E20" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
-    <hyperlink ref="E23" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
-    <hyperlink ref="E26" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
-    <hyperlink ref="E29" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5BBD1C52-098F-40DA-88A4-50C39110E03A}"/>
+    <hyperlink ref="E10" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{7543CBA5-4927-4A25-A5E3-63061D305676}"/>
+    <hyperlink ref="E21" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5659838B-8950-4628-AB3B-4F966499414E}"/>
+    <hyperlink ref="E24" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{C53175BE-D615-4996-98E7-F0F18FDB6588}"/>
+    <hyperlink ref="E27" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
+    <hyperlink ref="E30" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5BBD1C52-098F-40DA-88A4-50C39110E03A}"/>
     <hyperlink ref="A7" location="'ブラックボックス（UI）テスト'!A29" display="⑤部署名の重複チェック" xr:uid="{8EDA1AC3-5459-426F-983A-9291D61AB0A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/03_test/部署登録のテストケース.xlsx
+++ b/docs/03_test/部署登録のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61D0723-11EE-4B4B-9CC7-3CE281A4E5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CBBA09-BE9E-4A90-A2DB-198E5140C586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4951A3D-C49F-49FC-BC51-B2D2BF8D1643}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="45">
   <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
@@ -140,25 +140,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門登録(完了)画面に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>入力画面に遷移する</t>
     <rPh sb="0" eb="4">
       <t>ニュウリョクガメン</t>
@@ -169,51 +150,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門登録(入力)画面に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面上部の部門登録ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門名に「企画部」を入力して完了ボタンを押す</t>
-    <rPh sb="5" eb="7">
-      <t>キカク</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認画面に遷移する。</t>
     <rPh sb="0" eb="4">
       <t>カクニンガメン</t>
@@ -244,13 +180,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門登録単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>手順No</t>
     <rPh sb="0" eb="2">
       <t>テジュン</t>
@@ -319,28 +248,6 @@
   </si>
   <si>
     <t>①正常系を用いて一通り登録できる流れのチェック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門名に「情報システム部」を入力して完了ボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ブモンメイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>オ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -542,13 +449,24 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>⑥ホーム画面の部門一覧から新規登録に遷移</t>
+    <t>新規登録ボタンを押す</t>
+    <rPh sb="0" eb="4">
+      <t>シンキトウロク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署登録単体UIテスト 須崎千穂子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥ホーム画面の部署一覧から新規登録に遷移</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="7" eb="9">
-      <t>ブモン</t>
-    </rPh>
     <rPh sb="9" eb="11">
       <t>イチラン</t>
     </rPh>
@@ -561,10 +479,84 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門一覧を確認するボタンを押す</t>
+    <t>画面上部の部署登録ボタンを押す</t>
     <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署登録(入力)画面に遷移する</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名に「情報システム部」を入力して完了ボタンを押す</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署登録(完了)画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署名に「企画部」を入力して完了ボタンを押す</t>
+    <rPh sb="5" eb="7">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧を確認するボタンを押す</t>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
@@ -573,6 +565,42 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホーム画面の「部署一覧」を押す</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署の新規登録画面に遷移する</t>
+    <rPh sb="3" eb="9">
+      <t>シンキトウロクガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -682,20 +710,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2842381</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>376855</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>909675</xdr:rowOff>
+      <xdr:rowOff>555625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
+        <xdr:cNvPr id="14" name="図 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B591E3-1D13-796D-9B6E-48C22C8A319F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF10084E-D69A-9DB4-B8EC-3D1DED2F92AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -711,8 +739,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="2771825"/>
-          <a:ext cx="2842381" cy="909675"/>
+          <a:off x="9969500" y="2682876"/>
+          <a:ext cx="3250230" cy="555624"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -730,16 +758,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>30238</xdr:colOff>
+      <xdr:colOff>31750</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>867654</xdr:rowOff>
+      <xdr:rowOff>470978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
+        <xdr:cNvPr id="15" name="図 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6485023-2FAE-05B9-5C90-DB41192647CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC16A84-F0EC-6497-C1E7-C3114A1560A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -755,8 +783,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="4303889"/>
-          <a:ext cx="2902857" cy="867654"/>
+          <a:off x="9969500" y="4222750"/>
+          <a:ext cx="2905125" cy="470978"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -770,20 +798,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2812143</xdr:colOff>
+      <xdr:colOff>2841625</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>916635</xdr:rowOff>
+      <xdr:rowOff>481555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
+        <xdr:cNvPr id="16" name="図 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D21A306-0B53-0EE2-92CE-A04E2CBD910C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3736D2D4-AFA9-6D95-EF33-DF0B085026F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -799,8 +827,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="5835953"/>
-          <a:ext cx="2812143" cy="916634"/>
+          <a:off x="9969500" y="5762625"/>
+          <a:ext cx="2841625" cy="481555"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -817,17 +845,61 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2812143</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>859818</xdr:rowOff>
+      <xdr:rowOff>470978</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
+        <xdr:cNvPr id="17" name="図 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC7B8853-F4A9-C79A-71D1-B50FFC35BE23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{684664D3-F24B-4602-A06C-BF599A0352D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969500" y="7302500"/>
+          <a:ext cx="2905125" cy="470978"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2762251</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>603969</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{773EB340-B195-AADF-AA0F-2848AFCD50C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -843,8 +915,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="7368016"/>
-          <a:ext cx="2812143" cy="859818"/>
+          <a:off x="9969501" y="8842375"/>
+          <a:ext cx="2762250" cy="603969"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -857,21 +929,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>10079</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1150183</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2714625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>462948</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
+        <xdr:cNvPr id="25" name="図 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98D2D0F1-C46B-4310-5561-F31BA2278F09}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C08D7F5-14F1-BEE1-FA32-2FE207CA99B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -887,8 +959,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="8900080"/>
-          <a:ext cx="2882698" cy="1150182"/>
+          <a:off x="9969500" y="10382250"/>
+          <a:ext cx="2714625" cy="462948"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -901,21 +973,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2758586</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>846667</xdr:rowOff>
+      <xdr:colOff>2809875</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>428775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="26" name="図 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C3C454B-CFB3-072B-16D6-484C804F899F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F61C5D4-6A0C-D2D8-CFF2-94E177D1FC55}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -931,8 +1003,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="10432143"/>
-          <a:ext cx="2758586" cy="846667"/>
+          <a:off x="9969500" y="11922125"/>
+          <a:ext cx="2809875" cy="428775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -944,22 +1016,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>131031</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>141111</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>40317</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2809209</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>1267320</xdr:rowOff>
+      <xdr:rowOff>603251</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="27" name="図 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159E21D2-3285-EB5A-6941-8572E05838CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB909701-6B80-8805-F4F0-00D7AB548565}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -975,8 +1047,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10099523" y="13637381"/>
-          <a:ext cx="2781905" cy="1126209"/>
+          <a:off x="9969500" y="13462001"/>
+          <a:ext cx="2809209" cy="603250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,21 +1061,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2802065</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>943495</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>167602</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1111250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="28" name="図 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82412039-80EC-F0DE-9431-10009A9F6381}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79116A60-41AE-2B7E-BDDD-5C52202EAC62}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1019,8 +1091,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="11964207"/>
-          <a:ext cx="2802064" cy="943494"/>
+          <a:off x="9969501" y="15001875"/>
+          <a:ext cx="3040976" cy="1111250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1033,21 +1105,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2060223</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1471589</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>493697</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="29" name="図 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6CC79F0-157A-39F5-5AA2-15EF00861EDE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{104A93B2-76FE-3BA2-B301-92FA3A76FEE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1063,8 +1135,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="15028334"/>
-          <a:ext cx="2060223" cy="1471588"/>
+          <a:off x="9969500" y="17033875"/>
+          <a:ext cx="2873375" cy="493697"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1077,21 +1149,153 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>493697</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="図 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA4C05B1-9B44-421E-8016-4E122B80D342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969500" y="20494625"/>
+          <a:ext cx="2873375" cy="493697"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>493697</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="図 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F854530-C225-403C-85A7-94629FE635F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969500" y="24130000"/>
+          <a:ext cx="2873375" cy="493697"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>493697</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="図 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FEF2363-A33B-4C7A-AD00-EC00127C6F91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969500" y="27686000"/>
+          <a:ext cx="2873375" cy="493697"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2791984</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>970145</xdr:rowOff>
+      <xdr:colOff>2794001</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>494437</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="34" name="図 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{302B3641-2E1D-300B-256B-8730FC234488}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF6A87EF-450B-8769-27F1-CF8C2400F9E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1107,8 +1311,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="17054287"/>
-          <a:ext cx="2791984" cy="970144"/>
+          <a:off x="9969501" y="18542001"/>
+          <a:ext cx="2794000" cy="494436"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1121,153 +1325,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2791984</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>970144</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{156B6D19-56BD-45B9-A39A-28F60A937B9B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9968492" y="20491349"/>
-          <a:ext cx="2791984" cy="970144"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2791984</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>970144</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F10C29B-5AD0-45D1-92A3-D64ED651E16C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9968492" y="24109841"/>
-          <a:ext cx="2791984" cy="970144"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2791984</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>970144</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8145721C-2306-4562-AE84-F6D8C9090021}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9968492" y="27657778"/>
-          <a:ext cx="2791984" cy="970144"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2852460</xdr:colOff>
+      <xdr:colOff>2746375</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>862833</xdr:rowOff>
+      <xdr:rowOff>453411</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
+        <xdr:cNvPr id="35" name="図 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32AB8BB9-E74A-6849-6A3D-F29047FFCCB3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B62DF1-88BC-F866-2C31-C443365CD8CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1283,8 +1355,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="21993175"/>
-          <a:ext cx="2852459" cy="862833"/>
+          <a:off x="9969500" y="22002750"/>
+          <a:ext cx="2746375" cy="453411"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1301,17 +1373,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2791984</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22740</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>1172841</xdr:rowOff>
+      <xdr:rowOff>714375</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
+        <xdr:cNvPr id="36" name="図 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD72C78-2421-9029-6076-9A2349AB8CE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A94174A-E6A5-09F7-B87F-9634924564C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1327,8 +1399,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968492" y="25611667"/>
-          <a:ext cx="2791984" cy="1172841"/>
+          <a:off x="9969500" y="25638125"/>
+          <a:ext cx="2896115" cy="714375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1340,22 +1412,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2852460</xdr:colOff>
+      <xdr:colOff>2729671</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>1221109</xdr:rowOff>
+      <xdr:rowOff>777875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="37" name="図 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{030ECC85-1981-98E8-82AB-507CBB286C66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F5D90D8-82F7-E667-9EE2-855345761E28}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,8 +1443,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9968493" y="29129365"/>
-          <a:ext cx="2852459" cy="1221109"/>
+          <a:off x="9969500" y="29162375"/>
+          <a:ext cx="2729671" cy="777875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2857500</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1041970</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="図 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5135629B-3A2E-EB45-5B39-7A1C42050E95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969500" y="31384875"/>
+          <a:ext cx="2857500" cy="1041970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2801958</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>460375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="図 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC0D6AF-696D-DF1F-5EA3-5DA2E4CB3567}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9969499" y="32781876"/>
+          <a:ext cx="2801959" cy="460374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1693,14 +1853,14 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1708,7 +1868,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1716,7 +1876,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1724,7 +1884,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1732,7 +1892,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1740,7 +1900,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1748,7 +1908,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1761,18 +1921,18 @@
     </row>
     <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>1</v>
@@ -1789,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1800,7 +1960,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -1825,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1836,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1847,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1855,10 +2015,10 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1869,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="121" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1877,21 +2037,21 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1899,10 +2059,10 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1910,21 +2070,21 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1932,10 +2092,10 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1943,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
@@ -1951,13 +2111,13 @@
     </row>
     <row r="27" spans="1:5" ht="48.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1965,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1976,21 +2136,21 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="42.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1998,10 +2158,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="116" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -2009,20 +2169,51 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="110.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="110.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="37" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="38" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A10:D10"/>
@@ -2042,6 +2233,8 @@
     <hyperlink ref="E27" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{8F50C356-CD8B-4EE7-B15D-E7636317BBC5}"/>
     <hyperlink ref="E30" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{5BBD1C52-098F-40DA-88A4-50C39110E03A}"/>
     <hyperlink ref="A7" location="'ブラックボックス（UI）テスト'!A29" display="⑤部署名の重複チェック" xr:uid="{8EDA1AC3-5459-426F-983A-9291D61AB0A9}"/>
+    <hyperlink ref="E33" location="'ブラックボックス（UI）テスト'!A2" display="目次に戻る" xr:uid="{397DB45C-7375-40E9-A168-638FD0BC8A56}"/>
+    <hyperlink ref="A8" location="'ブラックボックス（UI）テスト'!A33" display="⑥ホーム画面の部門一覧から新規登録に遷移" xr:uid="{D6518813-CE37-4682-8185-5F0638D9CCA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
